--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104755_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104755_W33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5581</v>
+        <v>3.4293</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9178</v>
+        <v>2.6322</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6402</v>
+        <v>0.7971</v>
       </c>
       <c r="G2" t="n">
         <v>2.1019</v>
@@ -610,13 +610,13 @@
         <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>0.09039999999999999</v>
+        <v>-0.0384</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0468</v>
+        <v>-0.3324</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1372</v>
+        <v>0.294</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.771</v>
+        <v>2.8651</v>
       </c>
       <c r="E3" t="n">
         <v>0.6555</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1155</v>
+        <v>2.2096</v>
       </c>
       <c r="G3" t="n">
         <v>2.2715</v>
@@ -688,13 +688,13 @@
         <v>0.4553</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2718</v>
+        <v>0.3659</v>
       </c>
       <c r="T3" t="n">
         <v>0.0185</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2533</v>
+        <v>0.3474</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1933</v>
+        <v>1.681</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1301</v>
+        <v>0.9629</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0632</v>
+        <v>0.7181</v>
       </c>
       <c r="G4" t="n">
         <v>0.6077</v>
@@ -766,13 +766,13 @@
         <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6052</v>
+        <v>1.0929</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2505</v>
+        <v>0.0834</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3546</v>
+        <v>1.0096</v>
       </c>
       <c r="V4" t="n">
         <v>-0.7025</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.275</v>
+        <v>-0.7601</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6309</v>
+        <v>1.7185</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9059</v>
+        <v>-2.4786</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2747</v>
+        <v>0.9961</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8732</v>
+        <v>-0.6294</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.1478</v>
+        <v>1.6255</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7036</v>
+        <v>4.1323</v>
       </c>
       <c r="K5" t="n">
-        <v>5.1808</v>
+        <v>0.5204</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.4772</v>
+        <v>3.612</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.9783</v>
+        <v>-3.1362</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3077</v>
+        <v>-1.1497</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6706</v>
+        <v>-1.9865</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1382</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.5039</v>
+        <v>-3.6421</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3658</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8906</v>
+        <v>0.2728</v>
       </c>
       <c r="T5" t="n">
-        <v>1.184</v>
+        <v>-0.019</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7066</v>
+        <v>0.2919</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2472</v>
+        <v>0.7025</v>
       </c>
       <c r="W5" t="n">
         <v>1.2472</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9831</v>
+        <v>-0.8345</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9036</v>
+        <v>-2.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.8867</v>
+        <v>1.2459</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8836000000000001</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5022</v>
+        <v>-0.6378</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3813</v>
+        <v>-0.14</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8053</v>
+        <v>-1.4531</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8099</v>
+        <v>-0.7379</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9955</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9218</v>
+        <v>0.6754</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3077</v>
+        <v>0.1002</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6141</v>
+        <v>0.5752</v>
       </c>
       <c r="P6" t="n">
+        <v>1.1382</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-0.2276</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-1.3658</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.1382</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>0.153</v>
+        <v>0.0523</v>
       </c>
       <c r="T6" t="n">
-        <v>0.464</v>
+        <v>-0.3997</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3111</v>
+        <v>0.452</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.792</v>
+        <v>-1.2472</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.792</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0611</v>
+        <v>-0.8923</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1501</v>
+        <v>2.6179</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0891</v>
+        <v>-3.5103</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7776999999999999</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6378</v>
+        <v>0.5022</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.14</v>
+        <v>0.3813</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4531</v>
+        <v>3.8053</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7379</v>
+        <v>1.8099</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7151999999999999</v>
+        <v>1.9955</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6754</v>
+        <v>-2.9218</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1002</v>
+        <v>-1.3077</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5752</v>
+        <v>-1.6141</v>
       </c>
       <c r="P7" t="n">
+        <v>-0.2276</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.3658</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.1382</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-0.2276</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.3658</v>
-      </c>
       <c r="S7" t="n">
-        <v>-0.1743</v>
+        <v>0.2437</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4694</v>
+        <v>0.1784</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2951</v>
+        <v>0.0653</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2472</v>
+        <v>-1.792</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2472</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1608</v>
+        <v>-1.1806</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4119</v>
+        <v>-3.3746</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5727</v>
+        <v>2.1941</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9961</v>
+        <v>-0.7904</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6294</v>
+        <v>-1.562</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6255</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1323</v>
+        <v>-1.6092</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5204</v>
+        <v>-1.4898</v>
       </c>
       <c r="L8" t="n">
-        <v>3.612</v>
+        <v>-0.1194</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.1362</v>
+        <v>0.8189</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1497</v>
+        <v>-0.0722</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9865</v>
+        <v>0.8911</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.7316</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.6421</v>
+        <v>-2.5039</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9105</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1279</v>
+        <v>0.2927</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3256</v>
+        <v>-0.351</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1978</v>
+        <v>0.6437</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7025</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2472</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5447</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4314</v>
+        <v>-1.2226</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5628</v>
+        <v>-0.1285</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1314</v>
+        <v>-1.0941</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7904</v>
+        <v>-2.2747</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.562</v>
+        <v>3.8732</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7717000000000001</v>
+        <v>-6.1478</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6092</v>
+        <v>0.7036</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4898</v>
+        <v>5.1808</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1194</v>
+        <v>-4.4772</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8189</v>
+        <v>-2.9783</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0722</v>
+        <v>-1.3077</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8911</v>
+        <v>-1.6706</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6829</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.5039</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8211</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0418</v>
+        <v>0.9429</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5391</v>
+        <v>0.4246</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5809</v>
+        <v>0.5184</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0895</v>
+        <v>1.2472</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9752</v>
+        <v>-1.8325</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0499</v>
+        <v>-1.6249</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0747</v>
+        <v>-0.2076</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6406</v>
@@ -1234,13 +1234,13 @@
         <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1418</v>
+        <v>0.2845</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9758</v>
+        <v>-0.5508</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1176</v>
+        <v>0.8353</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9317</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0685</v>
+        <v>-3.194</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1787</v>
+        <v>-0.3983</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8898</v>
+        <v>-2.7957</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8524</v>
@@ -1312,13 +1312,13 @@
         <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6713</v>
+        <v>0.2031</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8364</v>
+        <v>-0.0561</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1651</v>
+        <v>0.2592</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0895</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5233</v>
+        <v>-4.3178</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.749</v>
+        <v>-6.324</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2258</v>
+        <v>2.0062</v>
       </c>
       <c r="G12" t="n">
         <v>0.409</v>
@@ -1390,13 +1390,13 @@
         <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0625</v>
+        <v>0.1429</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6785</v>
+        <v>-0.2535</v>
       </c>
       <c r="U12" t="n">
-        <v>0.616</v>
+        <v>0.3964</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5447</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.956</v>
+        <v>-6.259</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.040699999999999</v>
+        <v>-5.343699999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9152000000000005</v>
+        <v>-0.9153000000000002</v>
       </c>
       <c r="G13" t="n">
         <v>-0.06600000000000034</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2168000000000005</v>
+        <v>0.2168000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-0.2825000000000004</v>
@@ -1444,22 +1444,22 @@
         <v>11.5208</v>
       </c>
       <c r="K13" t="n">
-        <v>6.326399999999999</v>
+        <v>6.3264</v>
       </c>
       <c r="L13" t="n">
-        <v>5.1944</v>
+        <v>5.194400000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-11.5867</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.1096</v>
+        <v>-6.109599999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-5.4771</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.6908</v>
+        <v>-5.690799999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-19.3485</v>
@@ -1468,13 +1468,13 @@
         <v>13.658</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1586</v>
+        <v>3.8553</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.9546</v>
+        <v>-1.2576</v>
       </c>
       <c r="U13" t="n">
-        <v>5.113099999999998</v>
+        <v>5.1132</v>
       </c>
       <c r="V13" t="n">
         <v>-4.3579</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8944</v>
+        <v>5.1427</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9177</v>
+        <v>3.5099</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9767</v>
+        <v>1.6328</v>
       </c>
       <c r="G14" t="n">
         <v>2.6757</v>
@@ -1546,13 +1546,13 @@
         <v>2.7316</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4642</v>
+        <v>-0.2159</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.185</v>
+        <v>-0.5927</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7207</v>
+        <v>0.3768</v>
       </c>
       <c r="V14" t="n">
         <v>1.0895</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7767</v>
+        <v>4.4143</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4895</v>
+        <v>2.8449</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2871</v>
+        <v>1.5694</v>
       </c>
       <c r="G15" t="n">
         <v>3.1518</v>
@@ -1624,13 +1624,13 @@
         <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5132</v>
+        <v>0.1244</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4879</v>
+        <v>-0.1326</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0253</v>
+        <v>0.257</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0718</v>
+        <v>2.0883</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8044</v>
+        <v>-0.3604</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7326</v>
+        <v>2.4487</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1439</v>
+        <v>0.9305</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1761</v>
+        <v>0.485</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3199</v>
+        <v>0.4455</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9721</v>
+        <v>0.7722</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1551</v>
+        <v>0.5861</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8169</v>
+        <v>0.1862</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8282</v>
+        <v>0.1583</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3312</v>
+        <v>-0.1011</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.497</v>
+        <v>0.2593</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3658</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3658</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2647</v>
+        <v>-0.2276</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7428</v>
+        <v>-0.697</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4782</v>
+        <v>0.4694</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7025</v>
+        <v>0.7025</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0895</v>
+        <v>0.7025</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8049</v>
+        <v>1.6748</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3604</v>
+        <v>3.0937</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1653</v>
+        <v>-1.4189</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9305</v>
+        <v>1.1439</v>
       </c>
       <c r="H17" t="n">
-        <v>0.485</v>
+        <v>-0.1761</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4455</v>
+        <v>1.3199</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7722</v>
+        <v>1.9721</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5861</v>
+        <v>0.1551</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1862</v>
+        <v>1.8169</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1583</v>
+        <v>-0.8282</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1011</v>
+        <v>-0.3312</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2593</v>
+        <v>-0.497</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6829</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8211</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.511</v>
+        <v>-0.1323</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.697</v>
+        <v>0.0322</v>
       </c>
       <c r="U17" t="n">
-        <v>0.186</v>
+        <v>-0.1645</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7025</v>
+        <v>-0.7025</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7025</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9218</v>
+        <v>0.6146</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1081</v>
+        <v>1.1436</v>
       </c>
       <c r="F18" t="n">
-        <v>2.03</v>
+        <v>-0.529</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4326</v>
+        <v>0.2186</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2411</v>
+        <v>0.2096</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1916</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2043</v>
+        <v>1.1646</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7302</v>
+        <v>0.5688</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4741</v>
+        <v>0.5958</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.946</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4891</v>
+        <v>-0.3592</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2826</v>
+        <v>-0.5868</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.4145</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.6908</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2763</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2695</v>
+        <v>0.2579</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2559</v>
+        <v>-0.021</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5254</v>
+        <v>0.2788</v>
       </c>
       <c r="V18" t="n">
-        <v>1.6342</v>
+        <v>-0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6342</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7471</v>
+        <v>0.5108</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0252</v>
+        <v>-1.5819</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2781</v>
+        <v>2.0927</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2186</v>
+        <v>2.4326</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2096</v>
+        <v>1.2411</v>
       </c>
       <c r="I19" t="n">
-        <v>0.008999999999999999</v>
+        <v>1.1916</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1646</v>
+        <v>3.2043</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5688</v>
+        <v>1.7302</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5958</v>
+        <v>1.4741</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.946</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3592</v>
+        <v>-0.4891</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5868</v>
+        <v>-0.2826</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6829</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-5.6908</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6829</v>
+        <v>2.2763</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3903</v>
+        <v>-0.1416</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1394</v>
+        <v>-0.7297</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.5881</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5447</v>
+        <v>1.6342</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.2426</v>
       </c>
       <c r="E20" t="n">
-        <v>0.798</v>
+        <v>0.2058</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1211</v>
+        <v>0.0368</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3824</v>
@@ -2014,13 +2014,13 @@
         <v>2.5039</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2462</v>
+        <v>-0.1881</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3943</v>
+        <v>-0.1979</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1482</v>
+        <v>0.0097</v>
       </c>
       <c r="V20" t="n">
         <v>2.7237</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1484</v>
+        <v>-0.3993</v>
       </c>
       <c r="E21" t="n">
         <v>-0.2992</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1508</v>
+        <v>-0.1001</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5385</v>
@@ -2092,13 +2092,13 @@
         <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0048</v>
+        <v>-0.2462</v>
       </c>
       <c r="T21" t="n">
         <v>-0.6273</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6321</v>
+        <v>0.3812</v>
       </c>
       <c r="V21" t="n">
         <v>0.1578</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6949</v>
+        <v>-0.6636</v>
       </c>
       <c r="E22" t="n">
         <v>-0.929</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2341</v>
+        <v>0.2655</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8041</v>
@@ -2170,13 +2170,13 @@
         <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1185</v>
+        <v>-0.0871</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1394</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4769</v>
+        <v>-0.9891</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9444</v>
+        <v>-0.7075</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5325</v>
+        <v>-0.2816</v>
       </c>
       <c r="G23" t="n">
         <v>-1.68</v>
@@ -2248,13 +2248,13 @@
         <v>2.0487</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3009</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2547</v>
+        <v>-1.0178</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0462</v>
+        <v>0.2047</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5447</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9458</v>
+        <v>-1.7879</v>
       </c>
       <c r="E24" t="n">
         <v>-2.8576</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9118000000000001</v>
+        <v>1.0697</v>
       </c>
       <c r="G24" t="n">
         <v>-2.7866</v>
@@ -2326,13 +2326,13 @@
         <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2973</v>
+        <v>-0.1394</v>
       </c>
       <c r="T24" t="n">
         <v>-0.5576</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2603</v>
+        <v>0.4182</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.6715</v>
+        <v>-3.1025</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.6207</v>
+        <v>-3.1469</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0508</v>
+        <v>0.0444</v>
       </c>
       <c r="G25" t="n">
         <v>-3.2955</v>
@@ -2404,13 +2404,13 @@
         <v>2.0487</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1288</v>
+        <v>-0.5598</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9061</v>
+        <v>-0.4324</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2227</v>
+        <v>-0.1275</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1578</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>6.956099999999998</v>
+        <v>7.745699999999997</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9153999999999995</v>
+        <v>0.9154000000000004</v>
       </c>
       <c r="F26" t="n">
-        <v>6.0407</v>
+        <v>6.830400000000001</v>
       </c>
       <c r="G26" t="n">
         <v>0.06600000000000117</v>
@@ -2482,13 +2482,13 @@
         <v>19.3488</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.1584</v>
+        <v>-2.3687</v>
       </c>
       <c r="T26" t="n">
         <v>-5.1132</v>
       </c>
       <c r="U26" t="n">
-        <v>1.9545</v>
+        <v>2.7442</v>
       </c>
       <c r="V26" t="n">
         <v>4.358000000000001</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104755_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104755_W33.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.099600000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104755_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-3.7417</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
